--- a/excel/KSeF_IZ_Tool_template.xlsx
+++ b/excel/KSeF_IZ_Tool_template.xlsx
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1. 1_Detect: paste statement lines into A2:F (line_id, date, amount, currency, payer, free_text). Click Detect IDs. Results land in H:N as values.</t>
+          <t>1. 1_Detect: paste statement lines into A2:F (line_id, date, amount, currency, payer, free_text). Click Detect IDs. Results land in H:N as values; lines without a valid IZ / KSeF number turn red.</t>
         </is>
       </c>
     </row>
